--- a/data/trans_orig/IMC_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2007</t>
+          <t>Población con sobrepeso u obesidad en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>277654</t>
+          <t>274944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>321912</t>
+          <t>319501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73036</t>
+          <t>71069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105283</t>
+          <t>104645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>357981</t>
+          <t>358385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>410365</t>
+          <t>412802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>147591</t>
+          <t>150002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191849</t>
+          <t>194559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198569</t>
+          <t>199207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230816</t>
+          <t>232783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>362990</t>
+          <t>360553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415374</t>
+          <t>414970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>197010</t>
+          <t>196978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>234402</t>
+          <t>235670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109898</t>
+          <t>110033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147096</t>
+          <t>145232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>317424</t>
+          <t>318730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>376353</t>
+          <t>370478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127730</t>
+          <t>126462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165122</t>
+          <t>165154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221819</t>
+          <t>223683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>259017</t>
+          <t>258882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354694</t>
+          <t>360569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>413623</t>
+          <t>412317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>337599</t>
+          <t>339959</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>380776</t>
+          <t>381907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>61782</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86796</t>
+          <t>86135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>410288</t>
+          <t>408084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>463201</t>
+          <t>457678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161613</t>
+          <t>160482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>204790</t>
+          <t>202430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77883</t>
+          <t>78544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103336</t>
+          <t>102897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>243867</t>
+          <t>249390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296780</t>
+          <t>298984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>750483</t>
+          <t>753033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>818639</t>
+          <t>820119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>285411</t>
+          <t>288633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>340445</t>
+          <t>339611</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1061676</t>
+          <t>1057722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1144018</t>
+          <t>1141711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>407807</t>
+          <t>406327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>475963</t>
+          <t>473413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>368908</t>
+          <t>369742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>423942</t>
+          <t>420720</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>791782</t>
+          <t>794089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>874124</t>
+          <t>878078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166988</t>
+          <t>168765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204880</t>
+          <t>206438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>292235</t>
+          <t>289201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>337811</t>
+          <t>335224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>467315</t>
+          <t>470615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>532638</t>
+          <t>530415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137395</t>
+          <t>135837</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175287</t>
+          <t>173510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>220630</t>
+          <t>223217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>266206</t>
+          <t>269240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368078</t>
+          <t>370301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>433401</t>
+          <t>430101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55815</t>
+          <t>55821</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83655</t>
+          <t>84794</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>620039</t>
+          <t>621854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>688787</t>
+          <t>691812</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>687698</t>
+          <t>689740</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>763522</t>
+          <t>762516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212784</t>
+          <t>211645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240624</t>
+          <t>240618</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>537878</t>
+          <t>534853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>606626</t>
+          <t>604811</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>759582</t>
+          <t>760588</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>835406</t>
+          <t>833364</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1862922</t>
+          <t>1863126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1977920</t>
+          <t>1971863</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1520018</t>
+          <t>1518579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1631708</t>
+          <t>1632520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3420708</t>
+          <t>3413555</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3575929</t>
+          <t>3575398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1261264</t>
+          <t>1267321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1376262</t>
+          <t>1376058</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1700197</t>
+          <t>1699385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1811887</t>
+          <t>1813326</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2995160</t>
+          <t>2995691</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3150381</t>
+          <t>3157534</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2012</t>
+          <t>Población con sobrepeso u obesidad en 2012 (tasa de respuesta: 96,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>259958</t>
+          <t>258991</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>301351</t>
+          <t>300900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83142</t>
+          <t>83811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118949</t>
+          <t>119466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354093</t>
+          <t>354302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>410906</t>
+          <t>411332</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128524</t>
+          <t>128975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169917</t>
+          <t>170884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192466</t>
+          <t>191949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228273</t>
+          <t>227604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>330385</t>
+          <t>329959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>387198</t>
+          <t>386989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>255121</t>
+          <t>254872</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>296000</t>
+          <t>294546</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115881</t>
+          <t>119515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156115</t>
+          <t>158534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>385403</t>
+          <t>383399</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442053</t>
+          <t>442894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108056</t>
+          <t>109510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148935</t>
+          <t>149184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170456</t>
+          <t>168037</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210690</t>
+          <t>207056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>288574</t>
+          <t>287733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>345224</t>
+          <t>347228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>426459</t>
+          <t>428280</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>472037</t>
+          <t>472799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133548</t>
+          <t>132902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164204</t>
+          <t>164403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>567073</t>
+          <t>570826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>622786</t>
+          <t>625554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,42%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147229</t>
+          <t>146467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192807</t>
+          <t>190986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80355</t>
+          <t>80156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>111657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241038</t>
+          <t>238270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296751</t>
+          <t>292998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>746615</t>
+          <t>745959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>813681</t>
+          <t>811953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>350788</t>
+          <t>353599</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>408348</t>
+          <t>407459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1117231</t>
+          <t>1115826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1204738</t>
+          <t>1202303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328894</t>
+          <t>330622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>395960</t>
+          <t>396616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344584</t>
+          <t>345473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>402144</t>
+          <t>399333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>690768</t>
+          <t>693203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>778275</t>
+          <t>779680</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>301921</t>
+          <t>300509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>343533</t>
+          <t>342567</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>424947</t>
+          <t>424191</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>479751</t>
+          <t>481025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>741283</t>
+          <t>740987</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>808067</t>
+          <t>808819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151193</t>
+          <t>152159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192805</t>
+          <t>194217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>232579</t>
+          <t>231305</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>287383</t>
+          <t>288139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398990</t>
+          <t>398238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>465774</t>
+          <t>466070</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71360</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102619</t>
+          <t>100904</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>595220</t>
+          <t>594087</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>657242</t>
+          <t>660510</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>677380</t>
+          <t>677479</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>749278</t>
+          <t>749979</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163309</t>
+          <t>165024</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194568</t>
+          <t>193994</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>395333</t>
+          <t>392065</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>457355</t>
+          <t>458488</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>569225</t>
+          <t>568524</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>641123</t>
+          <t>641024</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2143837</t>
+          <t>2133197</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2255582</t>
+          <t>2251572</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1785081</t>
+          <t>1786480</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1902975</t>
+          <t>1909749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3953076</t>
+          <t>3959546</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4126117</t>
+          <t>4124519</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1100844</t>
+          <t>1104854</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1212589</t>
+          <t>1223229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1497407</t>
+          <t>1490633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1615301</t>
+          <t>1613902</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2630691</t>
+          <t>2632289</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2803732</t>
+          <t>2797262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2016</t>
+          <t>Población con sobrepeso u obesidad en 2016 (tasa de respuesta: 95,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>229258</t>
+          <t>228236</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>270950</t>
+          <t>271260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119542</t>
+          <t>115461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154342</t>
+          <t>153858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>356374</t>
+          <t>357239</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>413490</t>
+          <t>413583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152623</t>
+          <t>152313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>194315</t>
+          <t>195337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181494</t>
+          <t>181978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216294</t>
+          <t>220375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>345919</t>
+          <t>345826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>403035</t>
+          <t>402170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200133</t>
+          <t>198634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237698</t>
+          <t>237197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127393</t>
+          <t>128250</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165165</t>
+          <t>166676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>333965</t>
+          <t>337230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391768</t>
+          <t>391997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128857</t>
+          <t>129358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166422</t>
+          <t>167921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196641</t>
+          <t>195130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234413</t>
+          <t>233556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>336593</t>
+          <t>336364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394396</t>
+          <t>391131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>308121</t>
+          <t>308444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>352359</t>
+          <t>351900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79226</t>
+          <t>77726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104523</t>
+          <t>103148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>394574</t>
+          <t>391904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>445225</t>
+          <t>445700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>151076</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>194855</t>
+          <t>194532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>52800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76722</t>
+          <t>78222</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213699</t>
+          <t>213224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>264350</t>
+          <t>267020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>704738</t>
+          <t>707280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>770968</t>
+          <t>768034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>336262</t>
+          <t>337887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>395531</t>
+          <t>394852</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1059853</t>
+          <t>1060783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1146881</t>
+          <t>1148266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336357</t>
+          <t>339291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>402587</t>
+          <t>400045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>388111</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>447380</t>
+          <t>445755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>744086</t>
+          <t>742701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>831114</t>
+          <t>830184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>349780</t>
+          <t>349870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>398216</t>
+          <t>397202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>394836</t>
+          <t>399109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>448635</t>
+          <t>449060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>765311</t>
+          <t>765137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>835614</t>
+          <t>831882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,19%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190129</t>
+          <t>191143</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238565</t>
+          <t>238475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>239066</t>
+          <t>238641</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292865</t>
+          <t>288592</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>440432</t>
+          <t>444164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>510735</t>
+          <t>510909</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59062</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88028</t>
+          <t>88386</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>543128</t>
+          <t>540747</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>607787</t>
+          <t>604880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>608728</t>
+          <t>609825</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>682439</t>
+          <t>682256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>189571</t>
+          <t>189213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>218537</t>
+          <t>220006</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>396662</t>
+          <t>399569</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>461321</t>
+          <t>463702</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>599609</t>
+          <t>599792</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>673320</t>
+          <t>672223</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1924586</t>
+          <t>1931062</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2038297</t>
+          <t>2044057</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1680154</t>
+          <t>1673720</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1794296</t>
+          <t>1797583</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3635846</t>
+          <t>3641429</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3800466</t>
+          <t>3800974</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1228076</t>
+          <t>1222316</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1341787</t>
+          <t>1335311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1535086</t>
+          <t>1531799</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1649228</t>
+          <t>1655662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2795289</t>
+          <t>2794781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2959909</t>
+          <t>2954326</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2023</t>
+          <t>Población con sobrepeso u obesidad en 2023 (tasa de respuesta: 96,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>269039</t>
+          <t>267323</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>312298</t>
+          <t>314420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>134934</t>
+          <t>132778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168220</t>
+          <t>167242</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>412306</t>
+          <t>412115</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>467732</t>
+          <t>470471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184850</t>
+          <t>182728</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228109</t>
+          <t>229825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267333</t>
+          <t>268311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300619</t>
+          <t>302775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>464969</t>
+          <t>462230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>520395</t>
+          <t>520586</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>246988</t>
+          <t>244441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>288371</t>
+          <t>289424</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155335</t>
+          <t>154875</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187815</t>
+          <t>187962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>414039</t>
+          <t>413564</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>472281</t>
+          <t>470709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158109</t>
+          <t>157056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199492</t>
+          <t>202039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187106</t>
+          <t>186959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>219586</t>
+          <t>220046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349120</t>
+          <t>350692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407362</t>
+          <t>407837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>449992</t>
+          <t>448283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>615950</t>
+          <t>614138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64382</t>
+          <t>63748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84631</t>
+          <t>84241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>505962</t>
+          <t>505405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>721093</t>
+          <t>739422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43097</t>
+          <t>44909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209055</t>
+          <t>210764</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77148</t>
+          <t>77538</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97397</t>
+          <t>98031</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99733</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>314864</t>
+          <t>315421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>645474</t>
+          <t>651685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>719983</t>
+          <t>722353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>484426</t>
+          <t>485503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>770786</t>
+          <t>764049</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1180695</t>
+          <t>1180980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1488256</t>
+          <t>1483614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296018</t>
+          <t>293648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370527</t>
+          <t>364316</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190099</t>
+          <t>196836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>476459</t>
+          <t>475382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>488631</t>
+          <t>493273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>796192</t>
+          <t>795907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>278458</t>
+          <t>281125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>324422</t>
+          <t>325645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>477082</t>
+          <t>478047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>585799</t>
+          <t>578319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>775148</t>
+          <t>773626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>885884</t>
+          <t>886000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141145</t>
+          <t>139922</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187109</t>
+          <t>184442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184243</t>
+          <t>191723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292960</t>
+          <t>291995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349724</t>
+          <t>349608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>460460</t>
+          <t>461982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56798</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107413</t>
+          <t>106324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>371721</t>
+          <t>370418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>423485</t>
+          <t>421614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>441863</t>
+          <t>440699</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>515072</t>
+          <t>517195</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128470</t>
+          <t>129559</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179085</t>
+          <t>178282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>294218</t>
+          <t>296089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>345982</t>
+          <t>347285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>438514</t>
+          <t>436391</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>511723</t>
+          <t>512887</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2047609</t>
+          <t>2050258</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2452833</t>
+          <t>2412984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1776854</t>
+          <t>1767122</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2211758</t>
+          <t>2180609</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3864901</t>
+          <t>3865037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4444648</t>
+          <t>4472569</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,35%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>867293</t>
+          <t>907142</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1272517</t>
+          <t>1269868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1209125</t>
+          <t>1240274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1644029</t>
+          <t>1653761</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2296361</t>
+          <t>2268440</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2876108</t>
+          <t>2875972</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>274944</t>
+          <t>278526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>319501</t>
+          <t>321390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71069</t>
+          <t>73503</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104645</t>
+          <t>104460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358385</t>
+          <t>359864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>412802</t>
+          <t>414615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150002</t>
+          <t>148113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>194559</t>
+          <t>190977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199207</t>
+          <t>199392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>230349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>360553</t>
+          <t>358740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>414970</t>
+          <t>413491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>196978</t>
+          <t>196635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>235670</t>
+          <t>235763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110033</t>
+          <t>109935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145232</t>
+          <t>146756</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>318730</t>
+          <t>318394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>370478</t>
+          <t>371543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126462</t>
+          <t>126369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165154</t>
+          <t>165497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223683</t>
+          <t>222159</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258882</t>
+          <t>258980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>360569</t>
+          <t>359504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>412317</t>
+          <t>412653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>339959</t>
+          <t>339055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>381907</t>
+          <t>384011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61782</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86135</t>
+          <t>86965</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>408084</t>
+          <t>407884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>457678</t>
+          <t>461032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160482</t>
+          <t>158378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202430</t>
+          <t>203334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78544</t>
+          <t>77714</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102897</t>
+          <t>102405</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249390</t>
+          <t>246036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298984</t>
+          <t>299184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>753033</t>
+          <t>755979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>820119</t>
+          <t>824900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288633</t>
+          <t>289171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>339611</t>
+          <t>341263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1057722</t>
+          <t>1059748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1141711</t>
+          <t>1147764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>406327</t>
+          <t>401546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>473413</t>
+          <t>470467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369742</t>
+          <t>368090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>420720</t>
+          <t>420182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>794089</t>
+          <t>788036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878078</t>
+          <t>876052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>168765</t>
+          <t>167878</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>206438</t>
+          <t>204559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289201</t>
+          <t>289592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335224</t>
+          <t>339223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>470615</t>
+          <t>469095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>530415</t>
+          <t>530732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135837</t>
+          <t>137716</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173510</t>
+          <t>174397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223217</t>
+          <t>219218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>269240</t>
+          <t>268849</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370301</t>
+          <t>369984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430101</t>
+          <t>431621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55821</t>
+          <t>55971</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84794</t>
+          <t>83874</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>621854</t>
+          <t>619721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>691812</t>
+          <t>691003</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>689740</t>
+          <t>687777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>762516</t>
+          <t>763845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211645</t>
+          <t>212565</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240618</t>
+          <t>240468</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>534853</t>
+          <t>535662</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>604811</t>
+          <t>606944</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>760588</t>
+          <t>759259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>833364</t>
+          <t>835327</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1863126</t>
+          <t>1866229</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1971863</t>
+          <t>1975993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1518579</t>
+          <t>1521248</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1632520</t>
+          <t>1639066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3413555</t>
+          <t>3417958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3575398</t>
+          <t>3583166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1267321</t>
+          <t>1263191</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1376058</t>
+          <t>1372955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1699385</t>
+          <t>1692839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1813326</t>
+          <t>1810657</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2995691</t>
+          <t>2987923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3157534</t>
+          <t>3153131</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>258991</t>
+          <t>258680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>300900</t>
+          <t>300225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83811</t>
+          <t>82212</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119466</t>
+          <t>117071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354302</t>
+          <t>351702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>411332</t>
+          <t>410674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128975</t>
+          <t>129650</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>170884</t>
+          <t>171195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191949</t>
+          <t>194344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227604</t>
+          <t>229203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>329959</t>
+          <t>330617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>386989</t>
+          <t>389589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>254872</t>
+          <t>256453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>294546</t>
+          <t>297140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119515</t>
+          <t>118726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>158534</t>
+          <t>158112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>383399</t>
+          <t>384173</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442894</t>
+          <t>445149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109510</t>
+          <t>106916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149184</t>
+          <t>147603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168037</t>
+          <t>168459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>207056</t>
+          <t>207845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>287733</t>
+          <t>285478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>347228</t>
+          <t>346454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>428280</t>
+          <t>426457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>472799</t>
+          <t>474365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132902</t>
+          <t>133199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164403</t>
+          <t>164878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>570826</t>
+          <t>570370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>625554</t>
+          <t>626089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146467</t>
+          <t>144901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>190986</t>
+          <t>192809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80156</t>
+          <t>79681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>111360</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>238270</t>
+          <t>237735</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>292998</t>
+          <t>293454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>745959</t>
+          <t>745363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>811953</t>
+          <t>812318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>353599</t>
+          <t>353128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>407459</t>
+          <t>407880</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1115826</t>
+          <t>1113932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1202303</t>
+          <t>1203695</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>330622</t>
+          <t>330257</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>396616</t>
+          <t>397212</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345473</t>
+          <t>345052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>399333</t>
+          <t>399804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>693203</t>
+          <t>691811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>779680</t>
+          <t>781574</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>300509</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>342567</t>
+          <t>343321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>424191</t>
+          <t>426507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481025</t>
+          <t>483235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>740987</t>
+          <t>741950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>808819</t>
+          <t>807723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152159</t>
+          <t>151405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194217</t>
+          <t>194124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>231305</t>
+          <t>229095</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>288139</t>
+          <t>285823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398238</t>
+          <t>399334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>466070</t>
+          <t>465107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71934</t>
+          <t>71650</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100904</t>
+          <t>102419</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>594087</t>
+          <t>594286</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>660510</t>
+          <t>657845</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>677479</t>
+          <t>678486</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>749979</t>
+          <t>749397</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165024</t>
+          <t>163509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193994</t>
+          <t>194278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>392065</t>
+          <t>394730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>458488</t>
+          <t>458289</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>568524</t>
+          <t>569106</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>641024</t>
+          <t>640017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2133197</t>
+          <t>2137715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2251572</t>
+          <t>2251741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1786480</t>
+          <t>1789662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1909749</t>
+          <t>1909943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3959546</t>
+          <t>3956767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4124519</t>
+          <t>4118601</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1104854</t>
+          <t>1104685</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1223229</t>
+          <t>1218711</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1490633</t>
+          <t>1490439</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1613902</t>
+          <t>1610720</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2632289</t>
+          <t>2638207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2797262</t>
+          <t>2800041</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>228236</t>
+          <t>228896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>271260</t>
+          <t>270201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115461</t>
+          <t>117262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153858</t>
+          <t>154830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>357239</t>
+          <t>355610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>413583</t>
+          <t>413273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152313</t>
+          <t>153372</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>195337</t>
+          <t>194677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181978</t>
+          <t>181006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220375</t>
+          <t>218574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>345826</t>
+          <t>346136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>402170</t>
+          <t>403799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>198634</t>
+          <t>198004</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237197</t>
+          <t>237075</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>128250</t>
+          <t>128140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>166676</t>
+          <t>167419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>337230</t>
+          <t>337239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391997</t>
+          <t>396033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129358</t>
+          <t>129480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167921</t>
+          <t>168551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195130</t>
+          <t>194387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>233556</t>
+          <t>233666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>336364</t>
+          <t>332328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>391131</t>
+          <t>391122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>308444</t>
+          <t>308669</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>351900</t>
+          <t>350075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77726</t>
+          <t>79120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103148</t>
+          <t>103576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391904</t>
+          <t>397509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>445700</t>
+          <t>446379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151076</t>
+          <t>152901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>194532</t>
+          <t>194307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>52372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78222</t>
+          <t>76828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213224</t>
+          <t>212545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267020</t>
+          <t>261415</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>707280</t>
+          <t>706583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>768034</t>
+          <t>771688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>337887</t>
+          <t>337853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>394852</t>
+          <t>393639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1060783</t>
+          <t>1064933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1148266</t>
+          <t>1144019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339291</t>
+          <t>335637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>400045</t>
+          <t>400742</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>390003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>445755</t>
+          <t>445789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742701</t>
+          <t>746948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>830184</t>
+          <t>826034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>349870</t>
+          <t>352043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>397202</t>
+          <t>397089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>399109</t>
+          <t>397052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>449060</t>
+          <t>447580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>765137</t>
+          <t>765510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>831882</t>
+          <t>838060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191143</t>
+          <t>191256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238475</t>
+          <t>236302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>238641</t>
+          <t>240121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>288592</t>
+          <t>290649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>444164</t>
+          <t>437986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>510909</t>
+          <t>510536</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>59188</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88386</t>
+          <t>88286</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>540747</t>
+          <t>541364</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>604880</t>
+          <t>602630</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>609825</t>
+          <t>608062</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>682256</t>
+          <t>684202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>189213</t>
+          <t>189313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>220006</t>
+          <t>218411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>399569</t>
+          <t>401819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>463702</t>
+          <t>463085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>599792</t>
+          <t>597846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>672223</t>
+          <t>673986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1931062</t>
+          <t>1929476</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2044057</t>
+          <t>2039816</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1673720</t>
+          <t>1680746</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1797583</t>
+          <t>1795853</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3641429</t>
+          <t>3639473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3800974</t>
+          <t>3806908</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1222316</t>
+          <t>1226557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1335311</t>
+          <t>1336897</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1531799</t>
+          <t>1533529</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1655662</t>
+          <t>1648636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2794781</t>
+          <t>2788847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2954326</t>
+          <t>2956282</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>313447</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>267323</t>
+          <t>288310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>314420</t>
+          <t>336180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>150044</t>
+          <t>166364</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132778</t>
+          <t>147748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167242</t>
+          <t>185208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>440959</t>
+          <t>479810</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>412115</t>
+          <t>450359</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>470471</t>
+          <t>510686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>206232</t>
+          <t>225123</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182728</t>
+          <t>202390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229825</t>
+          <t>250260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>285509</t>
+          <t>309134</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268311</t>
+          <t>290290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302775</t>
+          <t>327750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>491742</t>
+          <t>534257</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>462230</t>
+          <t>503381</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>520586</t>
+          <t>563708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>497148</t>
+          <t>538570</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>497148</t>
+          <t>538570</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>497148</t>
+          <t>538570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>435553</t>
+          <t>475498</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>435553</t>
+          <t>475498</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>435553</t>
+          <t>475498</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>932701</t>
+          <t>1014067</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>932701</t>
+          <t>1014067</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>932701</t>
+          <t>1014067</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>269081</t>
+          <t>285348</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>244441</t>
+          <t>262296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289424</t>
+          <t>307445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>172373</t>
+          <t>192641</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154875</t>
+          <t>175804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187962</t>
+          <t>210459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>441454</t>
+          <t>477989</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>413564</t>
+          <t>448621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>470709</t>
+          <t>508305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,04%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>177399</t>
+          <t>191182</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>157056</t>
+          <t>169085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202039</t>
+          <t>214234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>202548</t>
+          <t>222044</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>186959</t>
+          <t>204226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220046</t>
+          <t>238881</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>379947</t>
+          <t>413225</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>350692</t>
+          <t>382909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407837</t>
+          <t>442593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>446480</t>
+          <t>476530</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>446480</t>
+          <t>476530</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>446480</t>
+          <t>476530</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>374921</t>
+          <t>414685</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>374921</t>
+          <t>414685</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>374921</t>
+          <t>414685</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>821401</t>
+          <t>891214</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>821401</t>
+          <t>891214</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>821401</t>
+          <t>891214</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>532058</t>
+          <t>316784</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>448283</t>
+          <t>294639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>614138</t>
+          <t>336573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74229</t>
+          <t>84761</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63748</t>
+          <t>73423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84241</t>
+          <t>96834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>606286</t>
+          <t>401545</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>505405</t>
+          <t>374869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>739422</t>
+          <t>424525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>126989</t>
+          <t>144969</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44909</t>
+          <t>125180</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210764</t>
+          <t>167114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87550</t>
+          <t>97455</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77538</t>
+          <t>85382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98031</t>
+          <t>108793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>214540</t>
+          <t>242424</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81404</t>
+          <t>219444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>315421</t>
+          <t>269100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>659047</t>
+          <t>461753</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>659047</t>
+          <t>461753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>659047</t>
+          <t>461753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161779</t>
+          <t>182216</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>161779</t>
+          <t>182216</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161779</t>
+          <t>182216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>820826</t>
+          <t>643969</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>820826</t>
+          <t>643969</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>820826</t>
+          <t>643969</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>686506</t>
+          <t>753857</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>651685</t>
+          <t>719858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>722353</t>
+          <t>793102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>592954</t>
+          <t>436173</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>485503</t>
+          <t>410403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>764049</t>
+          <t>461014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1279461</t>
+          <t>1190031</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1180980</t>
+          <t>1143601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1483614</t>
+          <t>1233973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>329495</t>
+          <t>357995</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293648</t>
+          <t>318750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364316</t>
+          <t>391994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>367931</t>
+          <t>405055</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196836</t>
+          <t>380214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>475382</t>
+          <t>430825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>697426</t>
+          <t>763050</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>493273</t>
+          <t>719108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>795907</t>
+          <t>809480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1016001</t>
+          <t>1111852</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1016001</t>
+          <t>1111852</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1016001</t>
+          <t>1111852</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>960885</t>
+          <t>841228</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>960885</t>
+          <t>841228</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>960885</t>
+          <t>841228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1976887</t>
+          <t>1953081</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1976887</t>
+          <t>1953081</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1976887</t>
+          <t>1953081</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>302895</t>
+          <t>343554</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>281125</t>
+          <t>316608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>325645</t>
+          <t>367089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>511745</t>
+          <t>496531</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>478047</t>
+          <t>471536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>578319</t>
+          <t>518691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>814639</t>
+          <t>840085</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>773626</t>
+          <t>808821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>886000</t>
+          <t>873305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>65,49%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>162672</t>
+          <t>203472</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139922</t>
+          <t>179937</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>184442</t>
+          <t>230418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>258297</t>
+          <t>289958</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191723</t>
+          <t>267798</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>291995</t>
+          <t>314953</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>420969</t>
+          <t>493430</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349608</t>
+          <t>460210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>461982</t>
+          <t>524694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>465567</t>
+          <t>547026</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>465567</t>
+          <t>547026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>465567</t>
+          <t>547026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>770042</t>
+          <t>786489</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>770042</t>
+          <t>786489</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>770042</t>
+          <t>786489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1235608</t>
+          <t>1333515</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1235608</t>
+          <t>1333515</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1235608</t>
+          <t>1333515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81364</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>54882</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106324</t>
+          <t>105728</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>397017</t>
+          <t>442184</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>370418</t>
+          <t>416779</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>421614</t>
+          <t>473112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>478381</t>
+          <t>519745</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>440699</t>
+          <t>481848</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>517195</t>
+          <t>557926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>154519</t>
+          <t>154811</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129559</t>
+          <t>126643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178282</t>
+          <t>177489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>320686</t>
+          <t>356149</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296089</t>
+          <t>325221</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347285</t>
+          <t>381554</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>475205</t>
+          <t>510960</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436391</t>
+          <t>472779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>512887</t>
+          <t>548857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,25%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>235883</t>
+          <t>232371</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>235883</t>
+          <t>232371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>235883</t>
+          <t>232371</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>717703</t>
+          <t>798333</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>717703</t>
+          <t>798333</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>717703</t>
+          <t>798333</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>953586</t>
+          <t>1030705</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>953586</t>
+          <t>1030705</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>953586</t>
+          <t>1030705</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2162819</t>
+          <t>2090550</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2050258</t>
+          <t>2031758</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2412984</t>
+          <t>2154657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1898362</t>
+          <t>1818655</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1767122</t>
+          <t>1768270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2180609</t>
+          <t>1874983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4061181</t>
+          <t>3909205</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3865037</t>
+          <t>3823891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4472569</t>
+          <t>3984624</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1157307</t>
+          <t>1277552</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>907142</t>
+          <t>1213445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1269868</t>
+          <t>1336344</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1522521</t>
+          <t>1679794</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1240274</t>
+          <t>1623466</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1653761</t>
+          <t>1730179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2679828</t>
+          <t>2957346</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2268440</t>
+          <t>2881927</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2875972</t>
+          <t>3042660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3320126</t>
+          <t>3368102</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3320126</t>
+          <t>3368102</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3320126</t>
+          <t>3368102</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3420883</t>
+          <t>3498449</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3420883</t>
+          <t>3498449</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3420883</t>
+          <t>3498449</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6741009</t>
+          <t>6866551</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6741009</t>
+          <t>6866551</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6741009</t>
+          <t>6866551</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
